--- a/data/trans_orig/P1435-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2007</t>
+          <t>Población con diagnóstico de dolor menstrual en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>46199</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>33590</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>60513</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1268914</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1254345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1281783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1254600</t>
+          <t>1254345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1281523</t>
+          <t>1281783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1268914</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1254600</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1281523</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1315113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1315113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1315113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1315113</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1315113</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1315113</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162412</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140195</t>
+          <t>140312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187939</t>
+          <t>185527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>162412</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>140195</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>187939</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1425261</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1402146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1447361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1399734</t>
+          <t>1402146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1447478</t>
+          <t>1447361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1425261</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1399734</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1447478</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>88,16%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1587673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1587673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1587673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1587673</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1587673</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1587673</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37928</t>
+          <t>39220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64981</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>51535</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>37928</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>64981</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410391</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>437192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411431</t>
+          <t>410391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>438484</t>
+          <t>437192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>424877</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>411431</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>438484</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>86,36%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>452</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>476412</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>476412</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>476412</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260146</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>229865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>234160</t>
+          <t>229865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293836</t>
+          <t>290809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>260146</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>234160</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>293836</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3119051</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3088388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3149332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3085361</t>
+          <t>3088388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3145037</t>
+          <t>3149332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3119051</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3085361</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3145037</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3379197</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3379197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3379197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2090,13 +1610,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2110,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2129,25 +1648,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2012</t>
+          <t>Población con diagnóstico de dolor menstrual en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +1670,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2167,17 +1679,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2248,41 +1749,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2305,13 +1771,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2326,37 +1785,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23175</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,45 +1845,10 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>14636</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>8294</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>23175</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>1,73%</t>
         </is>
@@ -2439,37 +1863,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1323161</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1314651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1329628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1314622</t>
+          <t>1314651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1329503</t>
+          <t>1329628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2504,42 +1928,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1323161</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1314622</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1329503</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2552,37 +1941,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1337797</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1337797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1337797</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2616,41 +2005,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1337797</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1337797</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1337797</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2669,37 +2023,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92925</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75323</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112337</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,42 +2088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>92925</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>75323</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>112337</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2782,37 +2101,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1661667</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1641727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1679369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1642255</t>
+          <t>1641727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1679269</t>
+          <t>1679369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,45 +2161,10 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1542</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1661667</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1642255</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1679269</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,6%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>95,71%</t>
         </is>
@@ -2895,37 +2179,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1754592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1754592</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1754592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2959,41 +2243,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1633</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1754592</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1754592</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1754592</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3012,37 +2261,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>42495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,45 +2321,10 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>29848</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>20858</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>42494</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>9,27%</t>
         </is>
@@ -3125,37 +2339,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>428783</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>416136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>438186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416137</t>
+          <t>416136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437773</t>
+          <t>438186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3190,42 +2404,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>428783</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>416137</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>437773</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -3238,37 +2417,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>458631</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>458631</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>458631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3302,41 +2481,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>458631</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>458631</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>458631</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3355,37 +2499,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137409</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>161531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113870</t>
+          <t>115768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163009</t>
+          <t>161531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,47 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>137409</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>113870</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>163009</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -3468,37 +2577,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3413611</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3389489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3435252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3388011</t>
+          <t>3389489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3437150</t>
+          <t>3435252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,47 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3159</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3413611</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3388011</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3437150</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -3581,37 +2655,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3551020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3551020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3551020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3645,41 +2719,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3551020</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3551020</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3551020</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3693,13 +2732,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3713,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3732,25 +2770,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2016</t>
+          <t>Población con diagnóstico de dolor menstrual en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +2792,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3770,17 +2801,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3851,41 +2871,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3908,13 +2893,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3929,37 +2907,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,47 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8598</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4042,37 +2985,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>888</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>990875</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>985151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>993705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>986062</t>
+          <t>985151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>993730</t>
+          <t>993705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,47 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>990875</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>986062</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>993730</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3063,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>892</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>994660</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>994660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>994660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4219,41 +3127,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>994660</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>994660</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>994660</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4272,37 +3145,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>59762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,42 +3210,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>43823</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>32214</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>58003</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -4385,37 +3223,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1944477</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1928538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1956113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1930297</t>
+          <t>1928538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1956086</t>
+          <t>1956113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,45 +3283,10 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1944477</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1930297</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1956086</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>98,38%</t>
         </is>
@@ -4498,37 +3301,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1988300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1988300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1988300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4562,41 +3365,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1988300</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1988300</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1988300</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4615,37 +3383,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>18779</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>11556</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>29532</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -4728,37 +3461,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530361</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>519744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519608</t>
+          <t>519744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537584</t>
+          <t>537686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>530361</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>519608</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>537584</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -4841,37 +3539,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>526</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549140</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4905,41 +3603,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>549140</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>549140</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>549140</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4958,37 +3621,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66388</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52108</t>
+          <t>53550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84129</t>
+          <t>84229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,45 +3681,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>66388</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>52108</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>84129</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
@@ -5071,37 +3699,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3465712</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3447871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3478550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3447971</t>
+          <t>3447871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3479992</t>
+          <t>3478550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,42 +3764,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3465712</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3447971</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3479992</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5184,37 +3777,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532100</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532100</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532100</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5248,41 +3841,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3532100</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3532100</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3532100</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5296,13 +3854,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -5316,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5335,25 +3892,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2023</t>
+          <t>Población con diagnóstico de dolor menstrual en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +3914,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5373,17 +3923,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5454,41 +3993,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5511,13 +4015,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5532,37 +4029,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +4074,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,47 +4089,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>10879</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>6243</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>17595</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5645,37 +4107,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>741705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>733714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>746376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +4152,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>734989</t>
+          <t>733714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>746341</t>
+          <t>746376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,47 +4167,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>741705</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>734989</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>746341</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5758,37 +4185,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>752584</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>752584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>752584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5822,41 +4249,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>752584</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>752584</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>752584</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5875,37 +4267,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189545</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +4312,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114451</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>429539</t>
+          <t>418143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,47 +4327,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>189545</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>114451</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>429539</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -5988,37 +4345,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2042887</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1814289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2121311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +4390,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1802893</t>
+          <t>1814289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2117981</t>
+          <t>2121311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,47 +4405,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2755</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2042887</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1802893</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2117981</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>91,51%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>80,76%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -6101,37 +4423,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2232432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2232432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2232432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6165,41 +4487,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2914</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2232432</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>2232432</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2232432</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6218,37 +4505,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66403</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +4550,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>52751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,47 +4565,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>66403</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>52203</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>82225</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -6331,37 +4583,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>917</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>591505</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>573493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>605157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +4628,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>575683</t>
+          <t>573493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605705</t>
+          <t>605157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,47 +4643,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>591505</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>575683</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>605705</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>87,5%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -6444,37 +4661,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>999</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657908</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6508,41 +4725,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>657908</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>657908</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>657908</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6561,37 +4743,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266826</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>484732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +4788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187183</t>
+          <t>187468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>570057</t>
+          <t>484732</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,47 +4803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>266826</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>187183</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>570057</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -6674,37 +4821,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3376098</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3158192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3455456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +4866,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3072867</t>
+          <t>3158192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3455741</t>
+          <t>3455456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,47 +4881,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3376098</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3072867</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3455741</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>84,35%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -6787,37 +4899,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3642924</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3642924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3642924</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6851,41 +4963,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3642924</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3642924</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3642924</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6899,13 +4976,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P1435-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>34671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>60656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>34671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60768</t>
+          <t>60656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1254345</t>
+          <t>1254457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1281783</t>
+          <t>1280442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1254345</t>
+          <t>1254457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1281783</t>
+          <t>1280442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140312</t>
+          <t>140408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>186841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140312</t>
+          <t>140408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>186841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1402146</t>
+          <t>1400832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1447361</t>
+          <t>1447265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1402146</t>
+          <t>1400832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1447361</t>
+          <t>1447265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39220</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66021</t>
+          <t>65720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39220</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66021</t>
+          <t>65720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410391</t>
+          <t>410692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437192</t>
+          <t>438816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>410391</t>
+          <t>410692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437192</t>
+          <t>438816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1314651</t>
+          <t>1313595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1329628</t>
+          <t>1328653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1314651</t>
+          <t>1313595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1329628</t>
+          <t>1328653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>73432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112865</t>
+          <t>112870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>73432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112865</t>
+          <t>112870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1641727</t>
+          <t>1641722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1679369</t>
+          <t>1681160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1641727</t>
+          <t>1641722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1679369</t>
+          <t>1681160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416136</t>
+          <t>416880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438186</t>
+          <t>439062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416136</t>
+          <t>416880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>438186</t>
+          <t>439062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115768</t>
+          <t>116768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>162341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115768</t>
+          <t>116768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>162341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3389489</t>
+          <t>3388679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3435252</t>
+          <t>3434252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3389489</t>
+          <t>3388679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3435252</t>
+          <t>3434252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>985151</t>
+          <t>985206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>993705</t>
+          <t>993704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>985151</t>
+          <t>985206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>993705</t>
+          <t>993704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>31476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59762</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>31476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59762</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1928538</t>
+          <t>1931015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1956113</t>
+          <t>1956824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1928538</t>
+          <t>1931015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1956113</t>
+          <t>1956824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29396</t>
+          <t>28080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29396</t>
+          <t>28080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519744</t>
+          <t>521060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537686</t>
+          <t>538002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519744</t>
+          <t>521060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537686</t>
+          <t>538002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>51813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>83600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>51813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>83600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3447871</t>
+          <t>3448500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3478550</t>
+          <t>3480287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3447871</t>
+          <t>3448500</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3478550</t>
+          <t>3480287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4034,32 +4034,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4069,32 +4069,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4112,32 +4112,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>741705</t>
+          <t>809421</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>733714</t>
+          <t>801268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746376</t>
+          <t>814027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>741705</t>
+          <t>809421</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>733714</t>
+          <t>801268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>746376</t>
+          <t>814027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -4190,17 +4190,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>820709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,32 +4272,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>189545</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111121</t>
+          <t>123212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>418143</t>
+          <t>171248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4307,32 +4307,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>189545</t>
+          <t>144311</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111121</t>
+          <t>123212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>418143</t>
+          <t>171248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2042887</t>
+          <t>2021685</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1814289</t>
+          <t>1994748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2121311</t>
+          <t>2042784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2042887</t>
+          <t>2021685</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1814289</t>
+          <t>1994748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2121311</t>
+          <t>2042784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2232432</t>
+          <t>2165996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2232432</t>
+          <t>2165996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2232432</t>
+          <t>2165996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2232432</t>
+          <t>2165996</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2232432</t>
+          <t>2165996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2232432</t>
+          <t>2165996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66403</t>
+          <t>73333</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84415</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4545,32 +4545,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66403</t>
+          <t>73333</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84415</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>591505</t>
+          <t>657061</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>573493</t>
+          <t>640211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605157</t>
+          <t>671194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>591505</t>
+          <t>657061</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573493</t>
+          <t>640211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605157</t>
+          <t>671194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4666,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>657908</t>
+          <t>730394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>657908</t>
+          <t>730394</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>657908</t>
+          <t>730394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657908</t>
+          <t>730394</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657908</t>
+          <t>730394</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657908</t>
+          <t>730394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4748,32 +4748,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187468</t>
+          <t>199788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>484732</t>
+          <t>260517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4783,32 +4783,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187468</t>
+          <t>199788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>484732</t>
+          <t>260517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -4826,32 +4826,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3376098</t>
+          <t>3488166</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3158192</t>
+          <t>3456582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3455456</t>
+          <t>3517311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,32 +4861,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3376098</t>
+          <t>3488166</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3158192</t>
+          <t>3456582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3455456</t>
+          <t>3517311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4904,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3642924</t>
+          <t>3717099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3642924</t>
+          <t>3717099</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3642924</t>
+          <t>3717099</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3642924</t>
+          <t>3717099</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3642924</t>
+          <t>3717099</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3642924</t>
+          <t>3717099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
